--- a/artfynd/A 61046-2023 artfynd.xlsx
+++ b/artfynd/A 61046-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135456974</v>
       </c>
       <c r="B2" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135456926</v>
       </c>
       <c r="B3" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61046-2023 artfynd.xlsx
+++ b/artfynd/A 61046-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135456974</v>
       </c>
       <c r="B2" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135456926</v>
       </c>
       <c r="B3" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61046-2023 artfynd.xlsx
+++ b/artfynd/A 61046-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135456974</v>
       </c>
       <c r="B2" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135456926</v>
       </c>
       <c r="B3" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61046-2023 artfynd.xlsx
+++ b/artfynd/A 61046-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135456974</v>
       </c>
       <c r="B2" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135456926</v>
       </c>
       <c r="B3" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
